--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/MMK_Analysis/MMK_Analysis.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/MMK_Analysis/MMK_Analysis.xlsx
@@ -475,9 +475,9 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
@@ -732,14 +732,14 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>32.57076322410779</v>
+        <v>34</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.043880972823945</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>k=10(ρ=+0.405)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
@@ -817,14 +817,14 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>34</v>
+        <v>25.59</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>1.328398</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.471); k=9(ρ=−0.494)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=−0.357); k=3(ρ=−0.497); k=6(ρ=+0.375); k=9(ρ=−0.402)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
@@ -994,7 +994,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.435); k=9(ρ=−0.526)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.596); k=6(ρ=+0.409); k=9(ρ=−0.385)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.509)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.358); k=9(ρ=−0.480)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=−0.373); k=4(ρ=+0.357); k=5(ρ=−0.426); k=6(ρ=+0.377); k=7(ρ=−0.353); k=9(ρ=−0.470); k=11(ρ=−0.361)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.576)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=−0.342)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
@@ -1837,14 +1837,14 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.582); k=2(ρ=+0.361); k=9(ρ=−0.432); k=10(ρ=−0.351)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.362)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
@@ -2007,14 +2007,14 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.360)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.376)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.382); k=11(ρ=+0.341)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=−0.397); k=5(ρ=−0.397); k=9(ρ=−0.445)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>k=6(ρ=−0.460); k=7(ρ=+0.411); k=9(ρ=−0.672)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
@@ -2942,14 +2942,14 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>k=6(ρ=+0.384); k=10(ρ=−0.479)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>k=10(ρ=−0.353)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
@@ -3112,14 +3112,14 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>30.04350146698373</v>
+        <v>19.93</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>1.098407255767618</v>
+        <v>1.656195</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=+0.405); k=6(ρ=+0.350)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>k=11(ρ=−0.404)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
@@ -3818,10 +3818,10 @@
         <v>0.7887</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>33.881</v>
+        <v>33.299</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.0037</v>
+        <v>1.0274</v>
       </c>
     </row>
     <row r="3">
@@ -3867,10 +3867,10 @@
         <v>-1.9012</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>33.74</v>
+        <v>29.889</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>1.0079</v>
+        <v>1.2591</v>
       </c>
     </row>
     <row r="4">
@@ -3916,10 +3916,10 @@
         <v>2.2536</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>32.668</v>
+        <v>31.911</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.0109</v>
+        <v>1.0547</v>
       </c>
     </row>
   </sheetData>
